--- a/HBS_vs_CCL_sverka.xlsx
+++ b/HBS_vs_CCL_sverka.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -2184,17 +2184,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-1401-3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2204,40 +2204,40 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NO GO</t>
+          <t>GO IF</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>190-38102-001, 190-38102-003, 190-38102-002, 190-38102-004, 190-38103-001, 190-38103-003, 190-38103-004, 190-38103-002</t>
+          <t>2LA006181-01, 2LA006181-02, 2LA006181-22, 2LA006181-23</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -2254,60 +2254,60 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>30-2849-1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>B735</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>736642-7, 736643-7, 736643-8, 736643-9, 736643-10, 736643-20</t>
+          <t>2LA006181-01, 2LA006181-02, 2LA006181-22, 2LA006181-23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -2324,22 +2324,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2348,36 +2348,36 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>736642-7, 736643-7, 736643-8, 736643-9, 736643-10, 736643-20</t>
+          <t>D717-01-100, 100865, 2013-BR, 3214-30, 3214-31, RPS1-B, 2013-1, BPS7-3 ...</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY PACK ASSEMBLY | BATTERY POWER SUPPLY | BATTERY ASSEMBLY</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24, 33, 25</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5, С5, C6</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,I, T,R,I</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -2394,17 +2394,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>30-1401-3</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2414,320 +2414,40 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2LA006181-01, 2LA006181-02, 2LA006181-22, 2LA006181-23</t>
+          <t>D717-01-100, 100865, 2013-BR, 3214-30, 3214-31, RPS1-B, 2013-1, BPS7-3 ...</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>REAR POSITION STROBE LIGHT</t>
+          <t>BATTERY PACK ASSEMBLY | BATTERY POWER SUPPLY | BATTERY ASSEMBLY</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24, 33, 25</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C5, С5, C6</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>T,R,I</t>
+          <t>T,I, T,R,I</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>30-2849-1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LIGHT ASSY - STROBE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>B735</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2LA006181-01, 2LA006181-02, 2LA006181-22, 2LA006181-23</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>REAR POSITION STROBE LIGHT</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>11</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>D717-01-100, 100865, 2013-BR, 3214-30, 3214-31, RPS1-B, 2013-1, BPS7-3 ...</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>BATTERY PACK ASSEMBLY | BATTERY POWER SUPPLY | BATTERY ASSEMBLY</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>24, 33, 25</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>C5, С5, C6</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>T,I, T,R,I</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>6</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>BA51015-XX, BA51012-XX, BA23044-XX, BA20703-XX, BA21775-XX, BA61016WG-XX</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>11</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>D717-01-100, 100865, 2013-BR, 3214-30, 3214-31, RPS1-B, 2013-1, BPS7-3 ...</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>BATTERY PACK ASSEMBLY | BATTERY POWER SUPPLY | BATTERY ASSEMBLY</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>24, 33, 25</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>C5, С5, C6</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>T,I, T,R,I</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N373"/>
+  <dimension ref="A1:N347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24053,7 +23773,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24125,7 +23845,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24197,7 +23917,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24269,7 +23989,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24061,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24413,7 +24133,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24485,7 +24205,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24277,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24629,7 +24349,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24421,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24773,7 +24493,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24845,7 +24565,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24917,7 +24637,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -24989,7 +24709,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25061,7 +24781,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25133,7 +24853,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25205,7 +24925,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25277,7 +24997,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25349,7 +25069,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25421,7 +25141,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25493,7 +25213,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25565,7 +25285,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -25582,17 +25302,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-1401-3</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -25602,42 +25322,42 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>NO GO</t>
+          <t>GO IF</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>190-38102-001</t>
+          <t>2LA006181-01</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -25654,17 +25374,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-1401-3</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -25674,42 +25394,42 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>NO GO</t>
+          <t>GO IF</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>190-38102-003</t>
+          <t>2LA006181-02</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -25726,17 +25446,17 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-1401-3</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -25746,42 +25466,42 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>NO GO</t>
+          <t>GO IF</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>190-38102-002</t>
+          <t>2LA006181-22</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -25798,17 +25518,17 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-1401-3</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -25818,42 +25538,42 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>NO GO</t>
+          <t>GO IF</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>190-38102-004</t>
+          <t>2LA006181-23</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -25870,22 +25590,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-2849-1</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B735</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -25895,37 +25615,37 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>190-38103-001</t>
+          <t>2LA006181-01</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -25942,22 +25662,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-2849-1</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B735</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -25967,37 +25687,37 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>190-38103-003</t>
+          <t>2LA006181-02</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -26014,22 +25734,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-2849-1</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B735</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26039,37 +25759,37 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>190-38103-004</t>
+          <t>2LA006181-22</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -26086,22 +25806,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>65C34812-7</t>
+          <t>30-2849-1</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>FLAP TRACK ASSY</t>
+          <t>LIGHT ASSY - STROBE</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B735</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26111,37 +25831,37 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>190-38103-002</t>
+          <t>2LA006181-23</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>Flap Track Rail</t>
+          <t>REAR POSITION STROBE LIGHT</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Goodrich</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>Flap Track ≈ Flap Track Rail; ATA различаются (27 vs 57)</t>
+          <t>Strobe light ≈ Rear Position Strobe Light</t>
         </is>
       </c>
     </row>
@@ -26158,62 +25878,62 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>736642-7</t>
+          <t>D717-01-100</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY PACK ASSEMBLY</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,I</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26230,62 +25950,62 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>736643-7</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>BRUCE INDUSTRIES</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26302,62 +26022,62 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>736643-8</t>
+          <t>2013-BR</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY ASSEMBLY</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>С5</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>BRUCE Aerospace</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26374,62 +26094,62 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>736643-9</t>
+          <t>3214-30</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>DIEHL</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26446,62 +26166,62 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>736643-10</t>
+          <t>3214-31</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>DIEHL</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26518,62 +26238,62 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>441921-5</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>FUEL CONTROL UNIT</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>GO IF</t>
+          <t>NO GO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>736643-20</t>
+          <t>RPS1-B</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26590,22 +26310,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -26615,37 +26335,37 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>736642-7</t>
+          <t>2013-1</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,I</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26662,22 +26382,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -26687,37 +26407,37 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>736643-7</t>
+          <t>BPS7-3</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26734,22 +26454,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -26759,37 +26479,37 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>736643-8</t>
+          <t>2013-1A</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>Battery Pack Assy</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26806,22 +26526,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -26831,37 +26551,37 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>736643-9</t>
+          <t>BPS7-2</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26878,22 +26598,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40678-2</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>MAIN BATTERY</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -26903,37 +26623,37 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>736643-10</t>
+          <t>ABS-2013-1A</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>Battery Pack Assy</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>AIRCRAFT BATTERY SHOP LLC</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -26950,22 +26670,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>3244871-8</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>FUEL CONTROL, MECHANICAL</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -26975,37 +26695,37 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>736643-20</t>
+          <t>D717-01-100</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Fuel Control Unit</t>
+          <t>BATTERY PACK ASSEMBLY</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>Zodiac Intertechnique</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T,I</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>Fuel Control ≈ Fuel Control Unit; ATA различаются (HBS 49/73 vs CCL 28)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27022,44 +26742,44 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>30-1401-3</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>737CL</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>NO GO</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>100865</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>BATTERY POWER SUPPLY</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>2LA006181-01</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>REAR POSITION STROBE LIGHT</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K338" t="inlineStr">
         <is>
           <t>C5</t>
@@ -27067,7 +26787,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>BRUCE INDUSTRIES</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27077,7 +26797,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27094,52 +26814,52 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>30-1401-3</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>737CL</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>NO GO</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>2013-BR</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>BATTERY ASSEMBLY</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>2LA006181-02</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>REAR POSITION STROBE LIGHT</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>С5</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>BRUCE Aerospace</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -27149,7 +26869,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27166,44 +26886,44 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>30-1401-3</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>737CL</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>NO GO</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>3214-30</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>2LA006181-22</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>REAR POSITION STROBE LIGHT</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K340" t="inlineStr">
         <is>
           <t>C5</t>
@@ -27211,7 +26931,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>DIEHL</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -27221,7 +26941,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27238,44 +26958,44 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>30-1401-3</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>737CL</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>NO GO</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>3214-31</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>2LA006181-23</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>REAR POSITION STROBE LIGHT</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K341" t="inlineStr">
         <is>
           <t>C5</t>
@@ -27283,7 +27003,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>DIEHL</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -27293,7 +27013,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27310,22 +27030,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>30-2849-1</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>B735</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -27335,27 +27055,27 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>2LA006181-01</t>
+          <t>RPS1-B</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>REAR POSITION STROBE LIGHT</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -27365,7 +27085,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27382,22 +27102,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>30-2849-1</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>B735</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -27407,37 +27127,37 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>2LA006181-02</t>
+          <t>2013-1</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>REAR POSITION STROBE LIGHT</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>T,R,I</t>
+          <t>T,I</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27454,22 +27174,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>30-2849-1</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>B735</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -27479,27 +27199,27 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>2LA006181-22</t>
+          <t>BPS7-3</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>REAR POSITION STROBE LIGHT</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -27509,7 +27229,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27526,22 +27246,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>30-2849-1</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LIGHT ASSY - STROBE</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>B735</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -27551,27 +27271,27 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>2LA006181-23</t>
+          <t>2013-1A</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>REAR POSITION STROBE LIGHT</t>
+          <t>Battery Pack Assy</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>Goodrich</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -27581,7 +27301,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>Strobe light ≈ Rear Position Strobe Light</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27598,12 +27318,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>40678-2</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>MAIN BATTERY</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -27613,7 +27333,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -27623,37 +27343,37 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>D717-01-100</t>
+          <t>BPS7-2</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>BATTERY PACK ASSEMBLY</t>
+          <t>BATTERY POWER SUPPLY</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>Collins Aerospace</t>
+          <t>RADIANT POWER CORP.</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>T,I</t>
+          <t>T,R,I</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -27670,12 +27390,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>40678-2</t>
+          <t>40176-7</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>MAIN BATTERY</t>
+          <t>STANDBY POWER STORAGE BATTERY</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -27685,7 +27405,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -27695,27 +27415,27 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>ABS-2013-1A</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>BATTERY POWER SUPPLY</t>
+          <t>Battery Pack Assy</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>BRUCE INDUSTRIES</t>
+          <t>AIRCRAFT BATTERY SHOP LLC</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -27725,1879 +27445,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>2013-BR</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>BATTERY ASSEMBLY</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>С5</t>
-        </is>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>BRUCE Aerospace</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>3214-30</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>DIEHL</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>3214-31</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>DIEHL</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>RPS1-B</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>2013-1</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>T,I</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>BPS7-3</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>2013-1A</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>Battery Pack Assy</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>BPS7-2</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>40678-2</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>MAIN BATTERY</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>ABS-2013-1A</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>Battery Pack Assy</t>
-        </is>
-      </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>AIRCRAFT BATTERY SHOP LLC</t>
-        </is>
-      </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>BA51015-XX</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>Fire Fighting Enterprises</t>
-        </is>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>BA51012-XX</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>Fire Fighting Enterprises</t>
-        </is>
-      </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N358" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>BA23044-XX</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>Fire Fighting Enterprises</t>
-        </is>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>BA20703-XX</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>Fire Fighting Enterprises</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>BA21775-XX</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>Fire Fighting Enterprises</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>863521-01</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>PORTABLE EXTINGUISHER</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>26-24</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>GO IF</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>BA61016WG-XX</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>Water Fire Extinguisher Assembly</t>
-        </is>
-      </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>Fire Fighting Enterprises</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t>Portable extinguisher ≈ Water Fire Extinguisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>D717-01-100</t>
-        </is>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>BATTERY PACK ASSEMBLY</t>
-        </is>
-      </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>Collins Aerospace</t>
-        </is>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>T,I</t>
-        </is>
-      </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>100865</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>BRUCE INDUSTRIES</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>2013-BR</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>BATTERY ASSEMBLY</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>С5</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>BRUCE Aerospace</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>3214-30</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>DIEHL</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>3214-31</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>DIEHL</t>
-        </is>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>RPS1-B</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>2013-1</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>BATTERY</t>
-        </is>
-      </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>T,I</t>
-        </is>
-      </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>BPS7-3</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>2013-1A</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>Battery Pack Assy</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>BPS7-2</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>BATTERY POWER SUPPLY</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t>RADIANT POWER CORP.</t>
-        </is>
-      </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Совпадение по наименованию (P/N другой)</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Средняя</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>40176-7</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>STANDBY POWER STORAGE BATTERY</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>737CL</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>NO GO</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>ABS-2013-1A</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>Battery Pack Assy</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t>AIRCRAFT BATTERY SHOP LLC</t>
-        </is>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>T,R,I</t>
-        </is>
-      </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>Совпадение по типу Battery (возможны разные применения/ATA)</t>
+          <t>Совпадение по типу Battery</t>
         </is>
       </c>
     </row>
@@ -29664,7 +27512,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -29674,7 +27522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -29706,84 +27554,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ENGINE FIRE EXTINGUISHER / FIRE EXTINGUISHER BOTTLE (HBS) vs Water Fire Extinguisher (CCL) — разные типы, не включал.</t>
+          <t>Fire extinguisher / portable extinguisher — не включать.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SENSOR-BLEED AIR OVERTEMP VALVE — не сопоставлял с Overtemperature Switch (это не switch).</t>
+          <t>Fuel Control и Flap Track — не включать как совпадения по наименованию.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RECIRCULATION FAN, HEAT EXCHANGER, MACHINE ASSY-AIR CYCLE — прямых аналогов по имени в CCL нет.</t>
+          <t>Battery / Main Battery / Standby Power Storage Battery — включать как тип Battery.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIGHT ASSY без типа, LIGHT-ANTICOLLISION, FLASH LIGHT — не сопоставлял.</t>
+          <t>SENSOR-BLEED AIR OVERTEMP VALVE — не сопоставлять с Overtemperature Switch.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PROPELLER BRAKE ≠ PROPELLER BLADE; WINDOW/PITOT HEAT MODULE ≠ SLIDING WINDOW.</t>
+          <t>RECIRCULATION FAN, HEAT EXCHANGER, AIR CYCLE — прямых аналогов по имени в CCL нет.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Общие ACTUATOR/PANEL/INDICATOR ASSY без уточнения — не включал.</t>
+          <t>LIGHT ASSY без типа, ANTICOLLISION, FLASH LIGHT — не сопоставлять.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Не включено / спорно</t>
+          <t>Правила сверки (по уточнению)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fuel Control и Flap Track — средняя уверенность из-за расхождения ATA.</t>
+          <t>PROPELLER BRAKE ≠ PROPELLER BLADE; слишком общие ACTUATOR/PANEL/INDICATOR ASSY — не включать.</t>
         </is>
       </c>
     </row>
